--- a/data/file_generation/input/data_116/20251101-20251130.xlsx
+++ b/data/file_generation/input/data_116/20251101-20251130.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zengyantao/Documents/办公标注/my_input/992e491c-94bd-43fe-b4b7-4bf49b3f51f6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zengyantao/Documents/办公标注/交付/input/data_116/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBB6B17-D5DD-C042-8E80-645EF149C1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E9F5DC-7825-F24A-82BC-4D6CF259D3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="43">
   <si>
     <t>交易日期</t>
   </si>
@@ -85,9 +85,6 @@
     <t>其他</t>
   </si>
   <si>
-    <t>美团酒店预订</t>
-  </si>
-  <si>
     <t>用户002</t>
   </si>
   <si>
@@ -146,6 +143,13 @@
   </si>
   <si>
     <t xml:space="preserve">   共 1 页      第 1 页</t>
+  </si>
+  <si>
+    <t>酒店预订</t>
+  </si>
+  <si>
+    <t>酒店预订</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -153,7 +157,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -218,7 +222,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -630,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>2317</v>
@@ -642,13 +646,13 @@
         <v>203602.93</v>
       </c>
       <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -712,7 +716,7 @@
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H5">
         <v>2317</v>
@@ -724,13 +728,13 @@
         <v>216891.47</v>
       </c>
       <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
         <v>22</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>23</v>
-      </c>
-      <c r="M5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -753,7 +757,7 @@
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6">
         <v>2317</v>
@@ -765,13 +769,13 @@
         <v>211891.47</v>
       </c>
       <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
         <v>26</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>27</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -794,7 +798,7 @@
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7">
         <v>2317</v>
@@ -806,13 +810,13 @@
         <v>166153.47</v>
       </c>
       <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" t="s">
         <v>30</v>
       </c>
-      <c r="L7" t="s">
-        <v>31</v>
-      </c>
       <c r="M7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -835,7 +839,7 @@
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8">
         <v>2317</v>
@@ -847,13 +851,13 @@
         <v>161084.5</v>
       </c>
       <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" t="s">
         <v>30</v>
       </c>
-      <c r="L8" t="s">
-        <v>31</v>
-      </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -876,7 +880,7 @@
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9">
         <v>2317</v>
@@ -888,13 +892,13 @@
         <v>149699.85</v>
       </c>
       <c r="K9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s">
         <v>30</v>
       </c>
-      <c r="L9" t="s">
-        <v>31</v>
-      </c>
       <c r="M9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -917,7 +921,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10">
         <v>2317</v>
@@ -929,13 +933,13 @@
         <v>130434.85</v>
       </c>
       <c r="K10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" t="s">
         <v>30</v>
       </c>
-      <c r="L10" t="s">
-        <v>31</v>
-      </c>
       <c r="M10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -958,7 +962,7 @@
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11">
         <v>2317</v>
@@ -970,13 +974,13 @@
         <v>129894.85</v>
       </c>
       <c r="K11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" t="s">
         <v>32</v>
       </c>
-      <c r="L11" t="s">
-        <v>33</v>
-      </c>
       <c r="M11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -999,7 +1003,7 @@
         <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12">
         <v>2317</v>
@@ -1011,13 +1015,13 @@
         <v>119034.85</v>
       </c>
       <c r="K12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" t="s">
         <v>34</v>
       </c>
-      <c r="L12" t="s">
-        <v>35</v>
-      </c>
       <c r="M12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1052,10 +1056,10 @@
         <v>119269.66</v>
       </c>
       <c r="K13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" t="s">
         <v>36</v>
-      </c>
-      <c r="L13" t="s">
-        <v>37</v>
       </c>
       <c r="M13" t="s">
         <v>20</v>
@@ -1122,7 +1126,7 @@
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H15">
         <v>2317</v>
@@ -1134,13 +1138,13 @@
         <v>132324.97</v>
       </c>
       <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
         <v>22</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>23</v>
-      </c>
-      <c r="M15" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1204,7 +1208,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H17">
         <v>2317</v>
@@ -1216,29 +1220,29 @@
         <v>146207.45000000001</v>
       </c>
       <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
         <v>22</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>23</v>
-      </c>
-      <c r="M17" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
         <v>38</v>
-      </c>
-      <c r="I18" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="N19" t="s">
         <v>40</v>
-      </c>
-      <c r="N19" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1412,13 +1416,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F8E8FDE-910F-4EEA-9797-2C5961CE0D61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{457CEEE6-B2FA-4E7D-8B9B-3C264E05B6D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{175B6B0B-E8AE-49A1-987F-7F02AB9FEF3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BF5B5D1-B6AC-4D66-9208-B4A01FD90657}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22C5ECE0-CB7B-48B2-BAF1-E7CF2FD1CB52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7E47415-8937-4A09-B852-211BA7B0CAAD}"/>
 </file>